--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -325,7 +325,7 @@
     <t xml:space="preserve">vampire</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.229 Patch 3</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">흡혈귀</t>
@@ -334,13 +334,13 @@
     <t xml:space="preserve">吸血鬼</t>
   </si>
   <si>
-    <t xml:space="preserve">(실험적) 흡혈귀는 예로부터 밤의 지배자로서 두려움의 대상이었던 종족으로, 뛰어난 신체능력과 지성을 갖고 있습니다. 흡혈귀들은 한밤중에는 특출난 능력을 발휘하지만, 햇볕과 불꽃에 취약하고 평범한 식사로는 배를 채울 수 없으며 항상 신선한 선혈에 굶주려 있습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Experimental) Vampires have long been feared as rulers of the night, gifted with both exceptional physical prowess and keen intellect. They display extraordinary abilities under the cover of darkness, yet remain vulnerable to sunlight and flame. Unable to sustain themselves on ordinary food, they are ever in hunger for fresh, living blood.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（実験的）吸血鬼は古来より夜の支配者として恐れられてきた種族で、高い身体能力と知性を備えています。彼らは闇夜の中で並外れた能力を発揮しますが、日の光と炎には脆弱で、通常の食事で栄養を満たすことができず、常に新鮮な生き血に飢えています。</t>
+    <t xml:space="preserve">흡혈귀는 예로부터 밤의 지배자로서 두려움의 대상이었던 종족으로, 뛰어난 신체능력과 지성을 갖고 있습니다. 흡혈귀들은 한밤중에는 특출난 능력을 발휘하지만, 햇볕과 불꽃에 취약하고 평범한 식사로는 배를 채울 수 없으며 항상 신선한 선혈에 굶주려 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vampires have long been feared as rulers of the night, gifted with both exceptional physical prowess and keen intellect. They display extraordinary abilities under the cover of darkness, yet remain vulnerable to sunlight and flame. Unable to sustain themselves on ordinary food, they are ever in hunger for fresh, living blood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吸血鬼は古来より夜の支配者として恐れられてきた種族で、高い身体能力と知性を備えています。彼らは闇夜の中で並外れた能力を発揮しますが、日の光と炎には脆弱で、通常の食事で栄養を満たすことができず、常に新鮮な生き血に飢えています。</t>
   </si>
   <si>
     <t xml:space="preserve">demigod</t>
@@ -1100,7 +1100,7 @@
   <fonts count="4">
     <font>
       <sz val="10"/>
-      <name val="나눔고딕"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -1317,9 +1317,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H92"/>
-  <sheetFormatPr defaultColWidth="7.9609375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="14.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="373">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -824,6 +824,18 @@
   </si>
   <si>
     <t xml:space="preserve">恐竜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에일리언</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアン</t>
   </si>
   <si>
     <t xml:space="preserve">cerberus</t>
@@ -1358,7 +1370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -2612,319 +2624,319 @@
         <v>267</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>23</v>
+        <v>268</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>267</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C65" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="D65" s="0" t="s">
         <v>271</v>
       </c>
-      <c r="D65" s="0" t="s">
-        <v>270</v>
-      </c>
       <c r="E65" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C66" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="D66" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="D66" s="0" t="s">
-        <v>273</v>
-      </c>
       <c r="E66" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C67" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="D67" s="0" t="s">
         <v>277</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>276</v>
-      </c>
       <c r="E67" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C68" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="D68" s="0" t="s">
         <v>280</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>279</v>
-      </c>
       <c r="E68" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C69" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="D69" s="0" t="s">
         <v>283</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>282</v>
-      </c>
       <c r="E69" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="D70" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="D70" s="0" t="s">
-        <v>285</v>
-      </c>
       <c r="E70" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="0" t="s">
-        <v>288</v>
-      </c>
       <c r="E71" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="D72" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="D72" s="0" t="s">
-        <v>291</v>
-      </c>
       <c r="E72" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="C73" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="D73" s="0" t="s">
         <v>295</v>
       </c>
-      <c r="D73" s="0" t="s">
-        <v>294</v>
-      </c>
       <c r="E73" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="C74" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="D74" s="0" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="0" t="s">
-        <v>297</v>
-      </c>
       <c r="E74" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C75" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="D75" s="0" t="s">
         <v>301</v>
       </c>
-      <c r="D75" s="0" t="s">
-        <v>300</v>
-      </c>
       <c r="E75" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C76" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="D76" s="0" t="s">
         <v>304</v>
       </c>
-      <c r="D76" s="0" t="s">
-        <v>303</v>
-      </c>
       <c r="E76" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C77" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="D77" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="D77" s="0" t="s">
-        <v>306</v>
-      </c>
       <c r="E77" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C78" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78" s="0" t="s">
         <v>310</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>309</v>
-      </c>
       <c r="E78" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="D79" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="D79" s="0" t="s">
-        <v>312</v>
-      </c>
       <c r="E79" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="D80" s="0" t="s">
         <v>316</v>
       </c>
-      <c r="D80" s="0" t="s">
-        <v>315</v>
-      </c>
       <c r="E80" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D81" s="0" t="s">
         <v>319</v>
       </c>
-      <c r="D81" s="0" t="s">
-        <v>318</v>
-      </c>
       <c r="E81" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>322</v>
+        <v>23</v>
       </c>
       <c r="C82" s="0" t="s">
         <v>323</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>324</v>
@@ -2935,183 +2947,183 @@
         <v>325</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>23</v>
+        <v>326</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>325</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C84" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="D84" s="0" t="s">
         <v>329</v>
       </c>
-      <c r="D84" s="0" t="s">
-        <v>328</v>
-      </c>
       <c r="E84" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C85" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="D85" s="0" t="s">
         <v>332</v>
       </c>
-      <c r="D85" s="0" t="s">
-        <v>331</v>
-      </c>
       <c r="E85" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C86" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="D86" s="0" t="s">
         <v>335</v>
       </c>
-      <c r="D86" s="0" t="s">
-        <v>334</v>
-      </c>
       <c r="E86" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C87" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="D87" s="0" t="s">
         <v>338</v>
       </c>
-      <c r="D87" s="0" t="s">
-        <v>337</v>
-      </c>
       <c r="E87" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>341</v>
+        <v>23</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>342</v>
       </c>
       <c r="D88" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="E88" s="0" t="s">
         <v>343</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B89" s="0" t="s">
         <v>345</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>23</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>346</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C90" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="D90" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>348</v>
-      </c>
       <c r="E90" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C91" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="D91" s="0" t="s">
         <v>352</v>
       </c>
-      <c r="D91" s="0" t="s">
-        <v>351</v>
-      </c>
       <c r="E91" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C92" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D92" s="0" t="s">
         <v>355</v>
       </c>
-      <c r="D92" s="0" t="s">
-        <v>354</v>
-      </c>
       <c r="E92" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>358</v>
+        <v>23</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>359</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>360</v>
@@ -3122,13 +3134,13 @@
         <v>361</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>107</v>
+        <v>362</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E94" s="0" t="s">
         <v>364</v>
@@ -3139,16 +3151,33 @@
         <v>365</v>
       </c>
       <c r="B95" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" s="0" t="s">
         <v>366</v>
       </c>
-      <c r="C95" s="0" t="s">
+      <c r="D95" s="0" t="s">
         <v>367</v>
-      </c>
-      <c r="D95" s="0" t="s">
-        <v>365</v>
       </c>
       <c r="E95" s="0" t="s">
         <v>368</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Race.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="375">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1142,6 +1142,12 @@
   </si>
   <si>
     <t xml:space="preserve">神</t>
+  </si>
+  <si>
+    <t xml:space="preserve">god_mani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -3177,6 +3183,23 @@
         <v>369</v>
       </c>
       <c r="E96" s="0" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="E97" s="0" t="s">
         <v>372</v>
       </c>
     </row>
